--- a/Dataset/IT/xlsx/ITAMed_2020.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2020.xlsx
@@ -761,7 +761,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Ossigenoterapia In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 1 Prova generale del 22/09/2020</t>
+          <t>Ossigenoterapia</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Colestiramina In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 2 Prova generale del 22/09/2020</t>
+          <t>Colestiramina</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Infusione fattore VIII In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 3 Prova generale del 22/09/2020</t>
+          <t>Infusione fattore VIII</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Esofagogastroduodenoscopia In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 4 Prova generale del 22/09/2020</t>
+          <t>Esofagogastroduodenoscopia</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Candidosi In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 5 Prova generale del 22/09/2020</t>
+          <t>Candidosi</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Ipotiroidismo primitivo In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 6 Prova generale del 22/09/2020</t>
+          <t>Ipotiroidismo primitivo</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Infliximab In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 7 Prova generale del 22/09/2020</t>
+          <t>Infliximab</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Ritmo sinusale con emiblocco fascicolare In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 8 Prova generale del 22/09/2020</t>
+          <t>Ritmo sinusale con emiblocco fascicolare</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>L'ipertensione arteriosa rappresenta un fattore di rischio per lo scompenso cardiaco In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 9 Prova generale del 22/09/2020</t>
+          <t>L'ipertensione arteriosa rappresenta un fattore di rischio per lo scompenso cardiaco</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Cefalea In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 10 Prova generale del 22/09/2020</t>
+          <t>Cefalea</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Salazopirina In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 11 Prova generale del 22/09/2020</t>
+          <t>Salazopirina</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>RM cerebrale In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 12 Prova generale del 22/09/2020</t>
+          <t>RM cerebrale</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Dosaggio calprotectina fecale In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 13 Prova generale del 22/09/2020</t>
+          <t>Dosaggio calprotectina fecale</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Malaria In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 14 Prova generale del 22/09/2020</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>&gt;1 e &lt;= 5 mm In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 15 Prova generale del 22/09/2020</t>
+          <t>&gt;1 e &lt;= 5 mm</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Colectomia totale con ileostomia In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 16 Prova generale del 22/09/2020</t>
+          <t>Colectomia totale con ileostomia</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Una vena, un'arteria e chorion In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 17 Prova generale del 22/09/2020</t>
+          <t>Una vena, un'arteria e chorion</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Zygote Intra Fallopian Transfer In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 18 Prova generale del 22/09/2020</t>
+          <t>Zygote Intra Fallopian Transfer</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Cisti ossea In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 19 Prova generale del 22/09/2020</t>
+          <t>Cisti ossea</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Tutte le altre risposte sono corrette In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 20 Prova generale del 22/09/2020</t>
+          <t>Tutte le altre risposte sono corrette</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Emorragia subaracnoidea In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 21 Prova generale del 22/09/2020</t>
+          <t>Emorragia subaracnoidea</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Cure termali In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 22 Prova generale del 22/09/2020</t>
+          <t>Cure termali</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Abolizione del fumo In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 23 Prova generale del 22/09/2020</t>
+          <t>Abolizione del fumo</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Epatica In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 24 Prova generale del 22/09/2020</t>
+          <t>Epatica</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Ecografia con mezzo di contrasto In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 25 Prova generale del 22/09/2020</t>
+          <t>Ecografia con mezzo di contrasto</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Immagine A: sequenza T2; Immagine B: sequenza T2 con mezzo di contrasto In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 26 Prova generale del 22/09/2020</t>
+          <t>Immagine A: sequenza T2; Immagine B: sequenza T2 con mezzo di contrasto</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Sovraslivellamento dell'emidiaframma sinistro In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 27 Prova generale del 22/09/2020</t>
+          <t>Sovraslivellamento dell'emidiaframma sinistro</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Esecuzione TC addome con mezzo di contrasto per valutare eziologia dell'insufficienza renale In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 28 Prova generale del 22/09/2020</t>
+          <t>Esecuzione TC addome con mezzo di contrasto per valutare eziologia dell'insufficienza renale</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Isoprenalina In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 29 Prova generale del 22/09/2020</t>
+          <t>Isoprenalina</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Nessuna delle altre risposte è corretta In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 30 Prova generale del 22/09/2020</t>
+          <t>Nessuna delle altre risposte è corretta</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>La vaccinazione anti difterite-tetano-pertosse non è più obbligatoria In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 31 Prova generale del 22/09/2020</t>
+          <t>La vaccinazione anti difterite-tetano-pertosse non è più obbligatoria</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>In merito all'interruzione volontaria di gravidanza nei primi 90 giorni dal concepimento (legge 194/1978) In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 32 Prova generale del 22/09/2020</t>
+          <t>In merito all'interruzione volontaria di gravidanza nei primi 90 giorni dal concepimento (legge 194/1978)</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Media e mediana coincidono In tutti i quesiti proposti la soluzione è la risposta alla lettera A) 33</t>
+          <t>Media e mediana coincidono</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_2020.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2020.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Cardiologia e Cardiochirurgia</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Ematologia; Farmacologia e Tossicologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Ematologia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Urologia; Farmacologia e Tossicologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Oncologia; Ortopedia e Traumatologia</t>
+          <t>Ematologia; Pediatria</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Dermatologia e Venereologia; Malattie Infettive</t>
+          <t>Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Ematologia; Oncologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Cardiologia e Cardiochirurgia</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Immunologia e Reumatologia; Farmacologia e Tossicologia</t>
+          <t>Immunologia e Reumatologia</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Ematologia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Oftalmologia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Pediatria; Oncologia</t>
+          <t>Pediatria; Ematologia</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Ematologia; Pediatria</t>
+          <t>Pediatria; Ematologia</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Anestesia e Rianimazione</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Endocrinologia</t>
+          <t>Endocrinologia; Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Farmacologia e Tossicologia</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Genetica Medica; Otorinolaringoiatria</t>
+          <t>Genetica Medica</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Otorinolaringoiatria; Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Neurologia e Neurochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Malattie Infettive</t>
+          <t>Malattie Infettive; Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Urologia</t>
+          <t>Urologia; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Pneumologia e Chirurgia Toracica</t>
+          <t>Pneumologia e Chirurgia Toracica; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Nefrologia; Farmacologia e Tossicologia</t>
+          <t>Nefrologia</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Nefrologia</t>
+          <t>Nefrologia; Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Igiene, Epidemiologia e Statistica; Malattie Infettive</t>
+          <t>Malattie Infettive</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_2020.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2020.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Immagine</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/IT/xlsx/ITAMed_2020.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2020.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.7890625" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -476,15 +476,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Tipo Domanda</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Immagine</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Categoria Immagine</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Percorso Immagine</t>
         </is>
@@ -544,7 +549,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -605,6 +615,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -663,6 +678,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -721,6 +741,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -779,6 +804,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -837,6 +867,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -895,6 +930,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -953,6 +993,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1011,6 +1056,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1066,7 +1116,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1127,6 +1182,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1185,6 +1245,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1243,6 +1308,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1301,6 +1371,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1359,6 +1434,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1417,6 +1497,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1475,6 +1560,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1533,6 +1623,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1591,6 +1686,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1649,6 +1749,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1707,6 +1812,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1765,6 +1875,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1823,6 +1938,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1881,6 +2001,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1939,6 +2064,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1997,6 +2127,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2055,6 +2190,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2113,6 +2253,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2171,6 +2316,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2229,6 +2379,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2287,6 +2442,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2345,6 +2505,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2403,6 +2568,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2461,6 +2631,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2521,10 +2696,15 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>images/2020/ssm20203813554.png</t>
         </is>
@@ -2589,10 +2769,15 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>images/2020/ssm20203813604.png</t>
         </is>
@@ -2655,6 +2840,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2713,6 +2903,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2771,6 +2966,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2829,6 +3029,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2887,6 +3092,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2945,6 +3155,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3003,6 +3218,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3061,6 +3281,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3119,6 +3344,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3177,6 +3407,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3235,6 +3470,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3293,6 +3533,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3351,6 +3596,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3409,6 +3659,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3467,6 +3722,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3525,6 +3785,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3583,6 +3848,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3641,6 +3911,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3699,6 +3974,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3757,6 +4037,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3815,6 +4100,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3873,6 +4163,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3931,6 +4226,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3989,6 +4289,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4047,6 +4352,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4105,6 +4415,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4163,6 +4478,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4221,6 +4541,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4279,6 +4604,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4337,6 +4667,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4395,6 +4730,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4453,6 +4793,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4511,6 +4856,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4569,6 +4919,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4627,6 +4982,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4685,6 +5045,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4743,6 +5108,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4801,6 +5171,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4859,6 +5234,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4917,6 +5297,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4975,6 +5360,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5033,6 +5423,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5091,6 +5486,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5149,6 +5549,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5207,6 +5612,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5265,6 +5675,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5323,6 +5738,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5381,6 +5801,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5439,6 +5864,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5497,6 +5927,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5557,10 +5992,15 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
           <t>Pelvic X-ray</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>images/2020/ssm20203816154.png</t>
         </is>
@@ -5623,6 +6063,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5681,6 +6126,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5739,6 +6189,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5797,6 +6252,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5857,10 +6317,15 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
           <t>Brain MRI</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>images/2020/ssm20203816404.png</t>
         </is>
@@ -5923,6 +6388,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5981,6 +6451,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6039,6 +6514,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6097,6 +6577,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6155,6 +6640,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6213,6 +6703,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6271,6 +6766,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6329,6 +6829,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6387,6 +6892,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6445,6 +6955,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6503,6 +7018,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6561,6 +7081,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6619,6 +7144,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6677,6 +7207,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6735,6 +7270,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6790,7 +7330,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6851,6 +7396,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6909,6 +7459,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6967,6 +7522,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7027,10 +7587,15 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
           <t>Brain MRI</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr">
+      <c r="O113" t="inlineStr">
         <is>
           <t>images/2020/ssm20203817404.png</t>
         </is>
@@ -7095,10 +7660,15 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
           <t>Chest CT scan</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr">
+      <c r="O114" t="inlineStr">
         <is>
           <t>images/2020/ssm20203817454.png</t>
         </is>
@@ -7161,6 +7731,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7219,6 +7794,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7277,6 +7857,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7335,6 +7920,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7393,6 +7983,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7451,6 +8046,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7509,6 +8109,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7567,6 +8172,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7625,6 +8235,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7683,6 +8298,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7741,6 +8361,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7799,6 +8424,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7857,6 +8487,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7915,6 +8550,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7973,6 +8613,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8031,6 +8676,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8089,6 +8739,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8147,6 +8802,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8205,6 +8865,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8263,6 +8928,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8321,6 +8991,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8379,6 +9054,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8437,6 +9117,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8495,6 +9180,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8553,6 +9243,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8611,6 +9306,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8667,6 +9367,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
